--- a/templates/05_Sales_Order.xlsx
+++ b/templates/05_Sales_Order.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SO-2026-001</t>
+          <t>SO-2026-020</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -511,15 +511,15 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>L02</t>
+          <t>L01</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -531,36 +531,36 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Multi-line order</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Acme Corp</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>Alpha Corp</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SO-2026-002</t>
+          <t>SO-2026-020</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SKU-B25</t>
+          <t>SKU-B04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>L01</t>
+          <t>L02</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -579,20 +579,24 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>MedSupply</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>Alpha Corp</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SO-2026-003</t>
+          <t>SO-2026-021</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SKU-A30</t>
+          <t>SKU-C30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -605,49 +609,65 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>GlobalPharma</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>Beta Ltd</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SO-2026-003</t>
+          <t>SO-2026-022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SKU-C30</t>
+          <t>SKU-B25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>L02</t>
+          <t>L01</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -655,17 +675,13 @@
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>GlobalPharma</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SO-2026-004</t>
+          <t>SO-2026-023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -679,14 +695,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -695,426 +713,17 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Bulk order</t>
+          <t>Urgent</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>BulkMed</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SO-2026-006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>SKU-A30</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>L01</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>On hold - customer request</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Acme Corp</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SO-2026-007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>SKU-B25</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>L02</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>200</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>MedSupply</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SO-2026-001</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>SKU-A30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>L01</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>500</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Released from hold</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Acme Corp</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SO-2026-007</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>SKU-B25</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>L01</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>650</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Qty revised +50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>MedSupply</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SO-2026-010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SKU-D01</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>L01</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>600</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Upside revision</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>BulkMed</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>SO-2026-011</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SKU-A30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>L01</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>250</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>New order - August</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>NewClient</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>SO-2026-011</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SKU-B04</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>L02</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>500</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>NewClient</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>SO-2026-012</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SKU-C30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>L01</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>300</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Start not before July 15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>FastCare</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>SO-2026-013</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>SKU-A10</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>L01</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>400</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Urgent - priority 1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>ClinicNet</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>Gamma Inc</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
         </is>
       </c>
     </row>
